--- a/backend/scripts/نموذج بيانات المدربين والمشرفين - أكاديمية الرضوان (Responses).xlsx
+++ b/backend/scripts/نموذج بيانات المدربين والمشرفين - أكاديمية الرضوان (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>Timestamp</t>
   </si>
@@ -40,42 +40,36 @@
     <t>رقم الهاتف الأساسي (رقم 1)</t>
   </si>
   <si>
+    <t>نوع الهوية</t>
+  </si>
+  <si>
+    <t>رقم الهوية / الوثيقة</t>
+  </si>
+  <si>
+    <t>تحميل صورة الواجهة الأمامية لوثيقة الهوية</t>
+  </si>
+  <si>
+    <t>تحميل صورة الواجهة الخلفية لوثيقة الهوية</t>
+  </si>
+  <si>
+    <t>العنوان بالتفصيل</t>
+  </si>
+  <si>
+    <t>الموقع الجغرافي (المدينة/المنطقة)</t>
+  </si>
+  <si>
+    <t>الدور في الأكاديمية</t>
+  </si>
+  <si>
+    <t>الراتب الشهري المتوقع/المتفق عليه</t>
+  </si>
+  <si>
+    <t>نبذة شخصية وسيرة ذاتية مختصرة (Bio)</t>
+  </si>
+  <si>
     <t>رقم هاتف إضافي (رقم 2) - اختياري</t>
   </si>
   <si>
-    <t>نوع الهوية</t>
-  </si>
-  <si>
-    <t>رقم الهوية / الوثيقة</t>
-  </si>
-  <si>
-    <t>تحميل صورة الواجهة الأمامية لوثيقة الهوية</t>
-  </si>
-  <si>
-    <t>تحميل صورة الواجهة الخلفية لوثيقة الهوية</t>
-  </si>
-  <si>
-    <t>العنوان بالتفصيل</t>
-  </si>
-  <si>
-    <t>الموقع الجغرافي (المدينة/المنطقة)</t>
-  </si>
-  <si>
-    <t>الدور في الأكاديمية</t>
-  </si>
-  <si>
-    <t>الراتب الشهري المتوقع/المتفق عليه</t>
-  </si>
-  <si>
-    <t>نبذة شخصية وسيرة ذاتية مختصرة (Bio)</t>
-  </si>
-  <si>
-    <t>تعيين كلمة مرور مؤقتة للنظام الداخلي</t>
-  </si>
-  <si>
-    <t>رقم هاتف إضافي (رقم 2) - اختياري 2</t>
-  </si>
-  <si>
     <t>mohamed</t>
   </si>
   <si>
@@ -112,9 +106,6 @@
     <t>good</t>
   </si>
   <si>
-    <t>mohamed123</t>
-  </si>
-  <si>
     <t>01556851539</t>
   </si>
   <si>
@@ -148,7 +139,25 @@
     <t>مشرف</t>
   </si>
   <si>
-    <t>hiphop120</t>
+    <t>mohamed.aboellil10100@gmail.com</t>
+  </si>
+  <si>
+    <t>أنثى</t>
+  </si>
+  <si>
+    <t>01025847099</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZZzglATpLbDRjQMq-klGoBOCyeiWTceQ</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ti1rak_3S0CXopb0MUf3oNqZSC5eqMqD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاسماعيلية ارض الجمعيات </t>
+  </si>
+  <si>
+    <t>ىخىخىخ</t>
   </si>
 </sst>
 </file>
@@ -223,11 +232,11 @@
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -326,8 +335,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:U3" displayName="Form_Responses" name="Form_Responses" id="1">
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:S4" displayName="Form_Responses" name="Form_Responses" id="1">
+  <tableColumns count="19">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="الاسم الأول" id="2"/>
     <tableColumn name="الاسم الثاني" id="3"/>
@@ -337,18 +346,16 @@
     <tableColumn name="تاريخ الميلاد" id="7"/>
     <tableColumn name="الجنس" id="8"/>
     <tableColumn name="رقم الهاتف الأساسي (رقم 1)" id="9"/>
-    <tableColumn name="رقم هاتف إضافي (رقم 2) - اختياري" id="10"/>
-    <tableColumn name="نوع الهوية" id="11"/>
-    <tableColumn name="رقم الهوية / الوثيقة" id="12"/>
-    <tableColumn name="تحميل صورة الواجهة الأمامية لوثيقة الهوية" id="13"/>
-    <tableColumn name="تحميل صورة الواجهة الخلفية لوثيقة الهوية" id="14"/>
-    <tableColumn name="العنوان بالتفصيل" id="15"/>
-    <tableColumn name="الموقع الجغرافي (المدينة/المنطقة)" id="16"/>
-    <tableColumn name="الدور في الأكاديمية" id="17"/>
-    <tableColumn name="الراتب الشهري المتوقع/المتفق عليه" id="18"/>
-    <tableColumn name="نبذة شخصية وسيرة ذاتية مختصرة (Bio)" id="19"/>
-    <tableColumn name="تعيين كلمة مرور مؤقتة للنظام الداخلي" id="20"/>
-    <tableColumn name="رقم هاتف إضافي (رقم 2) - اختياري 2" id="21"/>
+    <tableColumn name="نوع الهوية" id="10"/>
+    <tableColumn name="رقم الهوية / الوثيقة" id="11"/>
+    <tableColumn name="تحميل صورة الواجهة الأمامية لوثيقة الهوية" id="12"/>
+    <tableColumn name="تحميل صورة الواجهة الخلفية لوثيقة الهوية" id="13"/>
+    <tableColumn name="العنوان بالتفصيل" id="14"/>
+    <tableColumn name="الموقع الجغرافي (المدينة/المنطقة)" id="15"/>
+    <tableColumn name="الدور في الأكاديمية" id="16"/>
+    <tableColumn name="الراتب الشهري المتوقع/المتفق عليه" id="17"/>
+    <tableColumn name="نبذة شخصية وسيرة ذاتية مختصرة (Bio)" id="18"/>
+    <tableColumn name="رقم هاتف إضافي (رقم 2) - اختياري" id="19"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -557,17 +564,15 @@
   <cols>
     <col customWidth="1" min="1" max="8" width="18.88"/>
     <col customWidth="1" min="9" max="9" width="22.75"/>
-    <col customWidth="1" min="10" max="10" width="26.13"/>
-    <col customWidth="1" min="11" max="12" width="18.88"/>
-    <col customWidth="1" min="13" max="13" width="33.38"/>
-    <col customWidth="1" min="14" max="14" width="32.63"/>
-    <col customWidth="1" min="15" max="15" width="18.88"/>
-    <col customWidth="1" min="16" max="16" width="28.25"/>
-    <col customWidth="1" min="17" max="17" width="18.88"/>
-    <col customWidth="1" min="18" max="18" width="28.25"/>
-    <col customWidth="1" min="19" max="19" width="28.88"/>
-    <col customWidth="1" min="20" max="20" width="29.75"/>
-    <col customWidth="1" min="21" max="27" width="18.88"/>
+    <col customWidth="1" min="10" max="11" width="18.88"/>
+    <col customWidth="1" min="12" max="12" width="33.38"/>
+    <col customWidth="1" min="13" max="13" width="32.63"/>
+    <col customWidth="1" min="14" max="14" width="18.88"/>
+    <col customWidth="1" min="15" max="15" width="28.25"/>
+    <col customWidth="1" min="16" max="16" width="18.88"/>
+    <col customWidth="1" min="17" max="17" width="28.25"/>
+    <col customWidth="1" min="18" max="18" width="28.88"/>
+    <col customWidth="1" min="19" max="25" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -625,14 +630,8 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -640,60 +639,56 @@
         <v>46081.488529780094</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="G2" s="6">
         <v>46057.0</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="K2" s="5">
+        <v>3.0306171300114E13</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="7" t="s">
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="5">
-        <v>3.0306171300114E13</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="O2" s="10"/>
+      <c r="P2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="Q2" s="5">
+        <v>10000.0</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="R2" s="5">
-        <v>10000.0</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -701,64 +696,113 @@
         <v>46081.4909453125</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="G3" s="14">
         <v>46058.0</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="13">
+        <v>2.1160025711565E13</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>6000.0</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="11">
+        <v>46081.990097835645</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="14">
+        <v>46070.0</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="13">
-        <v>2.1160025711565E13</v>
-      </c>
-      <c r="M3" s="16" t="s">
+      <c r="K4" s="13">
+        <v>3.0306171300119E13</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="13">
-        <v>6000.0</v>
-      </c>
-      <c r="T3" s="13" t="s">
-        <v>45</v>
+      <c r="Q4" s="13">
+        <v>12000.0</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="M2"/>
-    <hyperlink r:id="rId2" ref="N2"/>
-    <hyperlink r:id="rId3" ref="M3"/>
-    <hyperlink r:id="rId4" ref="N3"/>
+    <hyperlink r:id="rId1" ref="L2"/>
+    <hyperlink r:id="rId2" ref="M2"/>
+    <hyperlink r:id="rId3" ref="L3"/>
+    <hyperlink r:id="rId4" ref="M3"/>
+    <hyperlink r:id="rId5" ref="L4"/>
+    <hyperlink r:id="rId6" ref="M4"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>